--- a/isms-core-framework/A.8-technological-controls/isms-a.8.24-use-of-cryptography/WKBK/90_workbooks/ISMS-IMP-A.8.24.3_Authentication_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.24-use-of-cryptography/WKBK/90_workbooks/ISMS-IMP-A.8.24.3_Authentication_20260208.xlsx
@@ -7003,7 +7003,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Example: Office 365 SSO - Azure AD</t>
+          <t>Example: Office 365 SSO - Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="T7" s="12" t="inlineStr">
